--- a/reports/Session_Live_Tests.xlsx
+++ b/reports/Session_Live_Tests.xlsx
@@ -1,14 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA60F4E7-E187-4AC2-BE19-932DD90BFCB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="📋 Résumé" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="🔍 Scénarios" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="🌐 Pages visitées" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="🎯 Actions" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="📡 Appels API" state="visible" r:id="rId8"/>
+    <sheet name="📋 Résumé" sheetId="1" r:id="rId1"/>
+    <sheet name="🔍 Scénarios" sheetId="2" r:id="rId2"/>
+    <sheet name="🌐 Pages visitées" sheetId="3" r:id="rId3"/>
+    <sheet name="🎯 Actions" sheetId="4" r:id="rId4"/>
+    <sheet name="📡 Appels API" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -347,35 +351,40 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFF"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-    </font>
-    <font>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFF"/>
-      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="12">
@@ -387,52 +396,52 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="16213E"/>
+        <fgColor rgb="FF16213E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="EEF2FF"/>
+        <fgColor rgb="FFEEF2FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="1B4332"/>
+        <fgColor rgb="FF1B4332"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="F5F7FF"/>
+        <fgColor rgb="FFF5F7FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEB9C"/>
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="C6EFCE"/>
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="457B9D"/>
+        <fgColor rgb="FF457B9D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="9B59B6"/>
+        <fgColor rgb="FF9B59B6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="E67E22"/>
+        <fgColor rgb="FFE67E22"/>
       </patternFill>
     </fill>
   </fills>
@@ -449,7 +458,7 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color rgb="E0E0E0"/>
+        <color rgb="FFE0E0E0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -459,9 +468,6 @@
   </cellStyleXfs>
   <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -508,6 +514,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -847,124 +856,124 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
-    <tabColor rgb="16213E"/>
+    <tabColor rgb="FF16213E"/>
   </sheetPr>
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-    </row>
-    <row r="2" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="22"/>
+    </row>
+    <row r="2" spans="1:2" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:2" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:2" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:2" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+    <row r="6" spans="1:2" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:2" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <v>16</v>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:2" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="4">
         <v>6</v>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:2" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:2" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="12" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:2" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="13" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+    <row r="13" spans="1:2" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:2" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="2">
         <v>3</v>
       </c>
     </row>
@@ -973,17 +982,17 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
-    <tabColor rgb="1B4332"/>
+    <tabColor rgb="FF1B4332"/>
   </sheetPr>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -992,87 +1001,87 @@
     <col min="5" max="5" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:5" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+    <row r="2" spans="1:5" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="9">
+    <row r="3" spans="1:5" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="8">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+    <row r="4" spans="1:5" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="6">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>28</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
-    <tabColor rgb="457B9D"/>
+    <tabColor rgb="FF457B9D"/>
   </sheetPr>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
@@ -1081,121 +1090,121 @@
     <col min="5" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:5" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+    <row r="2" spans="1:5" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="9">
+    <row r="3" spans="1:5" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="8">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+    <row r="4" spans="1:5" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="6">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="9">
+    <row r="5" spans="1:5" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="8">
         <v>4</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+    <row r="6" spans="1:5" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="6" t="s">
         <v>45</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
-    <tabColor rgb="9B59B6"/>
+    <tabColor rgb="FF9B59B6"/>
   </sheetPr>
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1204,308 +1213,308 @@
     <col min="5" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:5" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+    <row r="2" spans="1:5" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="9">
+    <row r="3" spans="1:5" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="8">
         <v>2</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+    <row r="4" spans="1:5" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="6">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="9">
+    <row r="5" spans="1:5" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="8">
         <v>4</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+    <row r="6" spans="1:5" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="9">
+    <row r="7" spans="1:5" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="8">
         <v>6</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="8" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="8" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
+    <row r="8" spans="1:5" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="6">
         <v>7</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="6" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="9" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="9">
+    <row r="9" spans="1:5" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="8">
         <v>8</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="8" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="10" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
-        <v>9</v>
-      </c>
-      <c r="B10" s="12" t="s">
+    <row r="10" spans="1:5" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="6">
+        <v>9</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="6" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="11" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="9">
+    <row r="11" spans="1:5" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
         <v>10</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="8" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="12" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
+    <row r="12" spans="1:5" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="6">
         <v>11</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="6" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="13" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="9">
+    <row r="13" spans="1:5" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
         <v>12</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="14" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
+    <row r="14" spans="1:5" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="6">
         <v>13</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="6" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="15" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="9">
+    <row r="15" spans="1:5" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
         <v>14</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="8" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="16" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
+    <row r="16" spans="1:5" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="6">
         <v>15</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="6" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="17" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="9">
+    <row r="17" spans="1:5" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="8">
         <v>16</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="8" t="s">
         <v>79</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
-    <tabColor rgb="E67E22"/>
+    <tabColor rgb="FFE67E22"/>
   </sheetPr>
   <dimension ref="A1:N7"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -1522,316 +1531,316 @@
     <col min="14" max="14" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:14" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="J1" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="L1" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="M1" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="N1" s="15" t="s">
+      <c r="N1" s="14" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+    <row r="2" spans="1:14" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D2" s="16">
         <v>200</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="H2" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="18" t="s">
+      <c r="H2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="K2" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="M2" s="19" t="s">
+      <c r="K2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" s="6" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="3" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="9">
+    <row r="3" spans="1:14" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="8">
         <v>2</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="16">
         <v>200</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="F3" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="M3" s="22" t="s">
+      <c r="F3" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N3" s="8" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+    <row r="4" spans="1:14" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="6">
         <v>3</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="16">
         <v>200</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="F4" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L4" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="M4" s="19" t="s">
+      <c r="F4" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="N4" s="6" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="9">
+    <row r="5" spans="1:14" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="8">
         <v>4</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="16">
         <v>200</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="H5" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="J5" s="21" t="s">
+      <c r="H5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="K5" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="L5" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="M5" s="22" t="s">
+      <c r="K5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="L5" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="M5" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="N5" s="9" t="s">
+      <c r="N5" s="8" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+    <row r="6" spans="1:14" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="16">
         <v>201</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="I6" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="J6" s="18" t="s">
+      <c r="I6" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="K6" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L6" s="19" t="s">
+      <c r="K6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="L6" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="M6" s="19" t="s">
+      <c r="M6" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="N6" s="7" t="s">
+      <c r="N6" s="6" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="9">
+    <row r="7" spans="1:14" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="8">
         <v>6</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="16">
         <v>200</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="H7" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="J7" s="21" t="s">
+      <c r="H7" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="K7" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="L7" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="M7" s="22" t="s">
+      <c r="K7" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="L7" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="M7" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="N7" s="9" t="s">
+      <c r="N7" s="8" t="s">
         <v>108</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>